--- a/output/pdf_financials_xlsx/WP.xlsx
+++ b/output/pdf_financials_xlsx/WP.xlsx
@@ -6205,40 +6205,40 @@
         <v>0.175395</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.365885</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.334365</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.323985</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.335069</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.356173</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.360377</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.359264</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.356339</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>0.357965</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>0.357965</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.275365</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.275365</v>
       </c>
       <c r="R92" s="3" t="n">
         <v>0</v>
@@ -11974,7 +11974,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
           <t>-</t>
@@ -15158,7 +15162,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -16644,7 +16652,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D78" t="inlineStr"/>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E78" t="inlineStr">
         <is>
           <t>-</t>
@@ -17820,7 +17832,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr"/>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E89" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/WP.xlsx
+++ b/output/pdf_financials_xlsx/WP.xlsx
@@ -1077,10 +1077,10 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.07632700000000001</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.06882099999999999</v>
       </c>
       <c r="J12" s="3" t="n">
         <v>0</v>
@@ -2084,10 +2084,10 @@
         <v>-0.109617</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.153993</v>
+        <v>-0.23032</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.125877</v>
+        <v>-0.194698</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.135255</v>
@@ -2206,10 +2206,10 @@
         <v>-0.109617</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.153993</v>
+        <v>-0.23032</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.125877</v>
+        <v>-0.194698</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>-0.135255</v>
@@ -2267,10 +2267,10 @@
         <v>-18.86783034667704</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-26.11086430889539</v>
+        <v>-39.05277686404439</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-18.40247828286225</v>
+        <v>-28.46370438377713</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>-19.03246868377579</v>
@@ -2457,13 +2457,13 @@
         <v>0.487643</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.523738</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.948051</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.046521</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>0.959249</v>
@@ -2579,13 +2579,13 @@
         <v>0.487643</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.523738</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.948051</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.046521</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>0.959249</v>
@@ -3311,13 +3311,13 @@
         <v>0.017588</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.546355</v>
+        <v>0.022617</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.9685319999999999</v>
+        <v>0.020481</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.068321</v>
+        <v>0.0218</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.015638</v>
@@ -14958,7 +14958,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -48128,7 +48128,7 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E384" t="inlineStr">

--- a/output/pdf_financials_xlsx/WP.xlsx
+++ b/output/pdf_financials_xlsx/WP.xlsx
@@ -2145,34 +2145,34 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.003054</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.007135</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.007532</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.004856</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.00492</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.003965</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.003171</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.002538</v>
       </c>
       <c r="P28" s="3" t="n">
-        <v>0</v>
+        <v>0.002225</v>
       </c>
       <c r="Q28" s="3" t="n">
-        <v>0</v>
+        <v>8e-06</v>
       </c>
       <c r="R28" s="3" t="n">
         <v>0</v>
@@ -2206,34 +2206,34 @@
         <v>-0.109617</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.23032</v>
+        <v>-0.227266</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.194698</v>
+        <v>-0.187563</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.135255</v>
+        <v>-0.127723</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.007223</v>
+        <v>-0.002367</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.032344</v>
+        <v>0.037264</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>0.143354</v>
+        <v>0.147319</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.07668</v>
+        <v>0.07985100000000001</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.752374</v>
+        <v>0.754912</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.333276</v>
+        <v>0.335501</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>0.268476</v>
+        <v>0.268484</v>
       </c>
       <c r="R29" s="3" t="n">
         <v>0.562619</v>
@@ -2267,34 +2267,34 @@
         <v>-18.86783034667704</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-39.05277686404439</v>
+        <v>-38.5349443677662</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-28.46370438377713</v>
+        <v>-27.42060927864893</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>-19.03246868377579</v>
+        <v>-17.97259988686478</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>-0.8678767838454523</v>
+        <v>-0.2844059736068373</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>3.437099506283567</v>
+        <v>3.959933094303452</v>
       </c>
       <c r="M30" s="3" t="n">
-        <v>13.18831953206002</v>
+        <v>13.55309265973429</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.236187733208515</v>
+        <v>7.535430707934704</v>
       </c>
       <c r="O30" s="3" t="n">
-        <v>67.3948017141301</v>
+        <v>67.62214610236052</v>
       </c>
       <c r="P30" s="3" t="n">
-        <v>21.8683460946148</v>
+        <v>22.01434241616366</v>
       </c>
       <c r="Q30" s="3" t="n">
-        <v>13.81777232451662</v>
+        <v>13.81818406403373</v>
       </c>
       <c r="R30" s="3" t="n">
         <v>27.47337477476598</v>
@@ -41298,7 +41298,7 @@
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
@@ -41367,10 +41367,10 @@
         </is>
       </c>
       <c r="R318" s="5" t="n">
-        <v>-0.002538</v>
+        <v>0.002538</v>
       </c>
       <c r="S318" s="5" t="n">
-        <v>-0.002225</v>
+        <v>0.002225</v>
       </c>
       <c r="T318" s="5" t="n">
         <v>8e-06</v>
@@ -42542,7 +42542,7 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
@@ -42606,10 +42606,10 @@
         </is>
       </c>
       <c r="Q330" s="5" t="n">
-        <v>-0.003171</v>
+        <v>0.003171</v>
       </c>
       <c r="R330" s="5" t="n">
-        <v>-0.002538</v>
+        <v>0.002538</v>
       </c>
       <c r="S330" s="5" t="n">
         <v>8e-06</v>
@@ -44098,7 +44098,7 @@
       </c>
       <c r="D345" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E345" t="inlineStr">
@@ -44152,10 +44152,10 @@
         </is>
       </c>
       <c r="O345" s="5" t="n">
-        <v>-0.00492</v>
+        <v>0.00492</v>
       </c>
       <c r="P345" s="5" t="n">
-        <v>-0.003965</v>
+        <v>0.003965</v>
       </c>
       <c r="Q345" s="5" t="n">
         <v>8e-06</v>
@@ -46056,7 +46056,7 @@
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
@@ -46105,10 +46105,10 @@
         </is>
       </c>
       <c r="N364" s="5" t="n">
-        <v>-0.004856</v>
+        <v>0.004856</v>
       </c>
       <c r="O364" s="5" t="n">
-        <v>-0.00492</v>
+        <v>0.00492</v>
       </c>
       <c r="P364" s="5" t="n">
         <v>9e-06</v>
@@ -46782,7 +46782,7 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E371" t="inlineStr">
@@ -46821,16 +46821,16 @@
         </is>
       </c>
       <c r="L371" s="5" t="n">
-        <v>-0.007135</v>
+        <v>0.007135</v>
       </c>
       <c r="M371" s="5" t="n">
-        <v>-0.007532</v>
+        <v>0.007532</v>
       </c>
       <c r="N371" s="5" t="n">
-        <v>-0.006027</v>
+        <v>0.006027</v>
       </c>
       <c r="O371" s="5" t="n">
-        <v>-0.004856</v>
+        <v>0.004856</v>
       </c>
       <c r="P371" t="inlineStr">
         <is>
@@ -48334,7 +48334,7 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>AmortizationOfIntangibles</t>
+          <t>DepreciationAmortizationDepletion</t>
         </is>
       </c>
       <c r="E386" t="inlineStr">
@@ -48368,10 +48368,10 @@
         </is>
       </c>
       <c r="K386" s="5" t="n">
-        <v>-0.003054</v>
+        <v>0.003054</v>
       </c>
       <c r="L386" s="5" t="n">
-        <v>-0.007135</v>
+        <v>0.007135</v>
       </c>
       <c r="M386" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/WP.xlsx
+++ b/output/pdf_financials_xlsx/WP.xlsx
@@ -1339,7 +1339,7 @@
         <v>0.143354</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>0.07668</v>
+        <v>0.81668</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>0.752374</v>
@@ -1400,7 +1400,7 @@
         <v>-0</v>
       </c>
       <c r="N17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.74</v>
       </c>
       <c r="O17" s="3" t="n">
         <v>0.09320000000000001</v>
@@ -1622,13 +1622,13 @@
         <v>-0.533366</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-0.47893</v>
+        <v>-0.5048</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-0.442799</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-0.509637</v>
+        <v>-0.492247</v>
       </c>
       <c r="F20" s="3" t="n">
         <v>-0.474234</v>
@@ -1683,13 +1683,13 @@
         <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>0.02587</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>0</v>
+        <v>-0.01739</v>
       </c>
       <c r="F21" s="3" t="n">
         <v>0</v>
@@ -2102,7 +2102,7 @@
         <v>0.143354</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>0.07668</v>
+        <v>0.81668</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>0.752374</v>
@@ -2224,7 +2224,7 @@
         <v>0.147319</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>0.07985100000000001</v>
+        <v>0.819851</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>0.754912</v>
@@ -2285,7 +2285,7 @@
         <v>13.55309265973429</v>
       </c>
       <c r="N30" s="3" t="n">
-        <v>7.535430707934704</v>
+        <v>77.36822834192402</v>
       </c>
       <c r="O30" s="3" t="n">
         <v>67.62214610236052</v>
@@ -2346,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>90.61076553852182</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>12.38745623851967</v>
@@ -4569,16 +4569,16 @@
         <v>0</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.051333</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.044275</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.042911</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.040708</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0</v>
@@ -22318,7 +22318,11 @@
           <t>Deferred income tax expense</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -25442,7 +25446,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -38520,7 +38528,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D291" t="inlineStr"/>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E291" t="inlineStr">
         <is>
           <t>-</t>
@@ -41606,7 +41618,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D321" t="inlineStr"/>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E321" t="inlineStr">
         <is>
           <t>-</t>
@@ -42850,7 +42866,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D333" t="inlineStr"/>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E333" t="inlineStr">
         <is>
           <t>-</t>
@@ -52556,7 +52576,11 @@
           <t>Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D426" t="inlineStr"/>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E426" t="inlineStr">
         <is>
           <t>-</t>
@@ -52656,7 +52680,11 @@
           <t>Net loss from discontinued operations</t>
         </is>
       </c>
-      <c r="D427" t="inlineStr"/>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E427" t="inlineStr">
         <is>
           <t>-</t>
@@ -54670,7 +54698,11 @@
           <t>Income from discontinued operations (note 10)</t>
         </is>
       </c>
-      <c r="D446" t="inlineStr"/>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E446" t="inlineStr">
         <is>
           <t>-</t>
